--- a/MLD01e_Results/Table04_AccuracyTableAwareness_v2.xlsx
+++ b/MLD01e_Results/Table04_AccuracyTableAwareness_v2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,28 +491,28 @@
         <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9014693171996543</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9304911955514366</v>
+        <v>0.9284386617100372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.962607861936721</v>
+        <v>0.9578139980824545</v>
       </c>
       <c r="G2" t="n">
-        <v>0.946277097078228</v>
+        <v>0.9428975932043416</v>
       </c>
       <c r="H2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>1004</v>
+        <v>999</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8954191875540191</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9276437847866419</v>
+        <v>0.9302973977695167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9587727708533078</v>
+        <v>0.959731543624161</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9429514380009429</v>
+        <v>0.9447852760736196</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>126</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8971477960242005</v>
+        <v>0.8997407087294728</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9301675977653632</v>
+        <v>0.9319664492078286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9578139980824545</v>
+        <v>0.9587727708533078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9437883797827114</v>
+        <v>0.945179584120983</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -599,25 +599,25 @@
         <v>0.898876404494382</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9294990723562152</v>
+        <v>0.9287037037037037</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.9616490891658677</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9448373408769448</v>
+        <v>0.9448893075836081</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="6">
@@ -631,16 +631,16 @@
         <v>210</v>
       </c>
       <c r="D6" t="n">
-        <v>0.898876404494382</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.931098696461825</v>
+        <v>0.9312906220984215</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9587727708533078</v>
+        <v>0.9616490891658677</v>
       </c>
       <c r="G6" t="n">
-        <v>0.944733112895607</v>
+        <v>0.9462264150943396</v>
       </c>
       <c r="H6" t="n">
         <v>40</v>
@@ -649,10 +649,10 @@
         <v>74</v>
       </c>
       <c r="J6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>252</v>
       </c>
       <c r="D7" t="n">
-        <v>0.902333621434745</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9297597042513863</v>
+        <v>0.9312906220984215</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9645254074784276</v>
+        <v>0.9616490891658677</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9468235294117647</v>
+        <v>0.9462264150943396</v>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I7" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K7" t="n">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
@@ -704,25 +704,25 @@
         <v>0.9014693171996543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9304911955514366</v>
+        <v>0.9296947271045328</v>
       </c>
       <c r="F8" t="n">
-        <v>0.962607861936721</v>
+        <v>0.9635666347075743</v>
       </c>
       <c r="G8" t="n">
-        <v>0.946277097078228</v>
+        <v>0.9463276836158192</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9014693171996543</v>
+        <v>0.8980121002592912</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9289012003693444</v>
+        <v>0.9270544783010157</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9645254074784276</v>
+        <v>0.962607861936721</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9463781749764817</v>
+        <v>0.9444967074317968</v>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K9" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="10">
@@ -806,28 +806,28 @@
         <v>420</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8980121002592912</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9286376274328082</v>
+        <v>0.9300373134328358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.9558964525407478</v>
       </c>
       <c r="G11" t="n">
-        <v>0.944392082940622</v>
+        <v>0.9427895981087471</v>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J11" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K11" t="n">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>0.902333621434745</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="E12" t="n">
-        <v>0.933768656716418</v>
+        <v>0.931098696461825</v>
       </c>
       <c r="F12" t="n">
-        <v>0.959731543624161</v>
+        <v>0.9587727708533078</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9465721040189126</v>
+        <v>0.944733112895607</v>
       </c>
       <c r="H12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J12" t="n">
         <v>43</v>
       </c>
-      <c r="I12" t="n">
-        <v>71</v>
-      </c>
-      <c r="J12" t="n">
-        <v>42</v>
-      </c>
       <c r="K12" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9014693171996543</v>
+        <v>0.905790838375108</v>
       </c>
       <c r="E13" t="n">
-        <v>0.932093023255814</v>
+        <v>0.9348230912476723</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.962607861936721</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9461756373937678</v>
+        <v>0.9485120453471895</v>
       </c>
       <c r="H13" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I13" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8997407087294728</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9335827876520112</v>
+        <v>0.9369708372530574</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9568552253116012</v>
+        <v>0.9549376797698945</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9450757575757576</v>
+        <v>0.9458689458689459</v>
       </c>
       <c r="H14" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I14" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K14" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="15">
@@ -946,16 +946,16 @@
         <v>168</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9049265341400173</v>
+        <v>0.9006050129645635</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9355742296918768</v>
+        <v>0.9352720450281425</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.9558964525407478</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9479659413434248</v>
+        <v>0.9454717875770507</v>
       </c>
       <c r="H15" t="n">
         <v>45</v>
@@ -964,10 +964,10 @@
         <v>69</v>
       </c>
       <c r="J15" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>210</v>
       </c>
       <c r="D16" t="n">
-        <v>0.902333621434745</v>
+        <v>0.9066551426101987</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9353932584269663</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9578139980824545</v>
+        <v>0.9616490891658677</v>
       </c>
       <c r="G16" t="n">
-        <v>0.946470866887731</v>
+        <v>0.9489120151371807</v>
       </c>
       <c r="H16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K16" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>252</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8997407087294728</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9311627906976744</v>
+        <v>0.9353327085285849</v>
       </c>
       <c r="F17" t="n">
-        <v>0.959731543624161</v>
+        <v>0.9568552253116012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9452313503305004</v>
+        <v>0.9459715639810427</v>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I17" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J17" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>294</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9031979256698358</v>
+        <v>0.902333621434745</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9370892018779343</v>
+        <v>0.9329608938547486</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9568552253116012</v>
+        <v>0.9606903163950143</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9468690702087287</v>
+        <v>0.9466225791213982</v>
       </c>
       <c r="H18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I18" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J18" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>336</v>
       </c>
       <c r="D19" t="n">
-        <v>0.902333621434745</v>
+        <v>0.905790838375108</v>
       </c>
       <c r="E19" t="n">
-        <v>0.933768656716418</v>
+        <v>0.9332096474953617</v>
       </c>
       <c r="F19" t="n">
-        <v>0.959731543624161</v>
+        <v>0.9645254074784276</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9465721040189126</v>
+        <v>0.9486091466289486</v>
       </c>
       <c r="H19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I19" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J19" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K19" t="n">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>378</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9006050129645635</v>
+        <v>0.9083837510803803</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.9350046425255338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9587727708533078</v>
+        <v>0.965484180249281</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9456264775413712</v>
+        <v>0.95</v>
       </c>
       <c r="H20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J20" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>420</v>
       </c>
       <c r="D21" t="n">
-        <v>0.905790838375108</v>
+        <v>0.9040622299049266</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9332096474953617</v>
+        <v>0.9347014925373134</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9645254074784276</v>
+        <v>0.9606903163950143</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9486091466289486</v>
+        <v>0.9475177304964539</v>
       </c>
       <c r="H21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>0.891961970613656</v>
+        <v>0.8928262748487468</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9234317343173432</v>
+        <v>0.9250693802035153</v>
       </c>
       <c r="F22" t="n">
-        <v>0.959731543624161</v>
+        <v>0.9587727708533078</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9412317818523742</v>
+        <v>0.9416195856873822</v>
       </c>
       <c r="H22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I22" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>84</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8928262748487468</v>
+        <v>0.8980121002592912</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9235023041474655</v>
+        <v>0.9270544783010157</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.962607861936721</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9417293233082706</v>
+        <v>0.9444967074317968</v>
       </c>
       <c r="H23" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I23" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J23" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>126</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9040622299049266</v>
+        <v>0.8980121002592912</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9283088235294118</v>
+        <v>0.9262672811059908</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9683604985618408</v>
+        <v>0.9635666347075743</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9479117785077429</v>
+        <v>0.9445488721804511</v>
       </c>
       <c r="H24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I24" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J24" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>168</v>
       </c>
       <c r="D25" t="n">
-        <v>0.898876404494382</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.9260628465804066</v>
       </c>
       <c r="F25" t="n">
-        <v>0.965484180249281</v>
+        <v>0.9606903163950143</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9450961989676209</v>
+        <v>0.9430588235294117</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I25" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J25" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>1007</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>210</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8936905790838375</v>
+        <v>0.8971477960242005</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9267161410018553</v>
+        <v>0.9293680297397769</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9578139980824545</v>
+        <v>0.9587727708533078</v>
       </c>
       <c r="G26" t="n">
-        <v>0.942008486562942</v>
+        <v>0.9438414346389806</v>
       </c>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I26" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>252</v>
       </c>
       <c r="D27" t="n">
-        <v>0.891961970613656</v>
+        <v>0.8867761452031115</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9226519337016574</v>
+        <v>0.9214417744916821</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9606903163950143</v>
+        <v>0.9558964525407478</v>
       </c>
       <c r="G27" t="n">
-        <v>0.941286989196806</v>
+        <v>0.9383529411764706</v>
       </c>
       <c r="H27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I27" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K27" t="n">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>294</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8910976663785652</v>
+        <v>0.891961970613656</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9233610341643582</v>
+        <v>0.921875</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9587727708533078</v>
+        <v>0.9616490891658677</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9407337723424271</v>
+        <v>0.9413420929141249</v>
       </c>
       <c r="H28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I28" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J28" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>336</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8936905790838375</v>
+        <v>0.8962834917891098</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9222323879231473</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9587727708533078</v>
+        <v>0.9664429530201343</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9420631182289213</v>
+        <v>0.9438202247191011</v>
       </c>
       <c r="H29" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I29" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J29" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30">
@@ -1471,22 +1471,22 @@
         <v>378</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8954191875540191</v>
+        <v>0.8971477960242005</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9244935543278084</v>
+        <v>0.9261992619926199</v>
       </c>
       <c r="F30" t="n">
         <v>0.962607861936721</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9431658055425082</v>
+        <v>0.9440526563234602</v>
       </c>
       <c r="H30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I30" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J30" t="n">
         <v>39</v>
@@ -1506,28 +1506,28 @@
         <v>420</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8980121002592912</v>
+        <v>0.8902333621434745</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9278445883441259</v>
+        <v>0.9232902033271719</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9616490891658677</v>
+        <v>0.9578139980824545</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9402352941176471</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I31" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K31" t="n">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>42</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9101123595505618</v>
+        <v>0.909248055315471</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9342592592592592</v>
+        <v>0.935813953488372</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9683301343570058</v>
+        <v>0.9654510556621881</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9509896324222432</v>
+        <v>0.9504015115729806</v>
       </c>
       <c r="H32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I32" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J32" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>84</v>
       </c>
       <c r="D33" t="n">
-        <v>0.909248055315471</v>
+        <v>0.9127052722558341</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9341983317886933</v>
+        <v>0.9360518999073216</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9673704414587332</v>
+        <v>0.9692898272552783</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9504950495049505</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="H33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I33" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K33" t="n">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>126</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9101123595505618</v>
+        <v>0.9075194468452895</v>
       </c>
       <c r="E34" t="n">
-        <v>0.933456561922366</v>
+        <v>0.9340761374187558</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9692898272552783</v>
+        <v>0.9654510556621881</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9510357815442562</v>
+        <v>0.9495044832468146</v>
       </c>
       <c r="H34" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I34" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>168</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9109766637856526</v>
+        <v>0.9118409680207433</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9327188940092166</v>
+        <v>0.9359925788497218</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9712092130518234</v>
+        <v>0.9683301343570058</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9515749882463563</v>
+        <v>0.9518867924528301</v>
       </c>
       <c r="H35" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I35" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J35" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K35" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>210</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9083837510803803</v>
+        <v>0.9118409680207433</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9341372912801484</v>
+        <v>0.9384328358208955</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9664107485604606</v>
+        <v>0.9654510556621881</v>
       </c>
       <c r="G36" t="n">
-        <v>0.95</v>
+        <v>0.9517502365184485</v>
       </c>
       <c r="H36" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I36" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>252</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9135695764909249</v>
+        <v>0.9066551426101987</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9369202226345084</v>
+        <v>0.9332096474953617</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9692898272552783</v>
+        <v>0.9654510556621881</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9528301886792453</v>
+        <v>0.9490566037735849</v>
       </c>
       <c r="H37" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I37" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J37" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K37" t="n">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>294</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9075194468452895</v>
+        <v>0.9109766637856526</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9324699352451434</v>
+        <v>0.9375582479030755</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9673704414587332</v>
+        <v>0.9654510556621881</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9495996231747527</v>
+        <v>0.9513002364066194</v>
       </c>
       <c r="H38" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I38" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>336</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9127052722558341</v>
+        <v>0.905790838375108</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9344413665743305</v>
+        <v>0.9331476323119777</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9712092130518234</v>
+        <v>0.9644913627639156</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9524705882352941</v>
+        <v>0.9485606418121756</v>
       </c>
       <c r="H39" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I39" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J39" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K39" t="n">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="40">
@@ -1821,16 +1821,16 @@
         <v>378</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9144338807260155</v>
+        <v>0.9135695764909249</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9353647276084949</v>
+        <v>0.9353049907578558</v>
       </c>
       <c r="F40" t="n">
-        <v>0.972168905950096</v>
+        <v>0.9712092130518234</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9534117647058824</v>
+        <v>0.9529190207156308</v>
       </c>
       <c r="H40" t="n">
         <v>45</v>
@@ -1839,10 +1839,10 @@
         <v>70</v>
       </c>
       <c r="J40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="41">
@@ -1856,22 +1856,22 @@
         <v>420</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9109766637856526</v>
+        <v>0.9118409680207433</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9335180055401662</v>
+        <v>0.9343807763401109</v>
       </c>
       <c r="F41" t="n">
         <v>0.9702495201535508</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9515294117647058</v>
+        <v>0.9519774011299436</v>
       </c>
       <c r="H41" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I41" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J41" t="n">
         <v>31</v>
@@ -1891,28 +1891,28 @@
         <v>42</v>
       </c>
       <c r="D42" t="n">
-        <v>0.891961970613656</v>
+        <v>0.8945548833189283</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9273066169617894</v>
+        <v>0.9307116104868914</v>
       </c>
       <c r="F42" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9408983451536643</v>
+        <v>0.9421800947867298</v>
       </c>
       <c r="H42" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I42" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="43">
@@ -1961,28 +1961,28 @@
         <v>126</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8902333621434745</v>
+        <v>0.8945548833189283</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9279700654817586</v>
+        <v>0.9275092936802974</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9520153550863724</v>
+        <v>0.9577735124760077</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9398389388915206</v>
+        <v>0.9423984891406988</v>
       </c>
       <c r="H44" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I44" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K44" t="n">
-        <v>992</v>
+        <v>998</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>168</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8962834917891098</v>
+        <v>0.8859118409680208</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9292364990689013</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9577735124760077</v>
+        <v>0.9481765834932822</v>
       </c>
       <c r="G45" t="n">
-        <v>0.943289224952741</v>
+        <v>0.9373814041745731</v>
       </c>
       <c r="H45" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I45" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J45" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K45" t="n">
-        <v>998</v>
+        <v>988</v>
       </c>
     </row>
     <row r="46">
@@ -2034,25 +2034,25 @@
         <v>0.8928262748487468</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9289719626168225</v>
+        <v>0.925</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9539347408829175</v>
+        <v>0.9587332053742802</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9412878787878788</v>
+        <v>0.941564561734213</v>
       </c>
       <c r="H46" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I46" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J46" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>252</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8945548833189283</v>
+        <v>0.8910976663785652</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9267161410018553</v>
+        <v>0.9280373831775701</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9587332053742802</v>
+        <v>0.9529750479846449</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9424528301886792</v>
+        <v>0.9403409090909091</v>
       </c>
       <c r="H47" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I47" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J47" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K47" t="n">
-        <v>999</v>
+        <v>993</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>294</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8893690579083837</v>
+        <v>0.8867761452031115</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9271028037383178</v>
+        <v>0.9237209302325582</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9520153550863724</v>
+        <v>0.9529750479846449</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.9381199811053378</v>
       </c>
       <c r="H48" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I48" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K48" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="49">
@@ -2139,25 +2139,25 @@
         <v>0.8945548833189283</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9283054003724395</v>
+        <v>0.9275092936802974</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9568138195777351</v>
+        <v>0.9577735124760077</v>
       </c>
       <c r="G49" t="n">
-        <v>0.94234404536862</v>
+        <v>0.9423984891406988</v>
       </c>
       <c r="H49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I49" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K49" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="50">
@@ -2171,28 +2171,28 @@
         <v>378</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8945548833189283</v>
+        <v>0.8936905790838375</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9267161410018553</v>
+        <v>0.9274418604651162</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9587332053742802</v>
+        <v>0.9568138195777351</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9424528301886792</v>
+        <v>0.9418989135569201</v>
       </c>
       <c r="H50" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I50" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J50" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K50" t="n">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="51">
@@ -2206,28 +2206,28 @@
         <v>420</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8971477960242005</v>
+        <v>0.8945548833189283</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9293023255813954</v>
+        <v>0.9299065420560748</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9587332053742802</v>
+        <v>0.95489443378119</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9437883797827114</v>
+        <v>0.9422348484848485</v>
       </c>
       <c r="H51" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I51" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J51" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K51" t="n">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="52">
@@ -2241,28 +2241,28 @@
         <v>42</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8841832324978393</v>
+        <v>0.8772687986171133</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9195933456561922</v>
+        <v>0.9182156133828996</v>
       </c>
       <c r="F52" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9481765834932822</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9369114877589454</v>
+        <v>0.9329556185080264</v>
       </c>
       <c r="H52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I52" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J52" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K52" t="n">
-        <v>995</v>
+        <v>988</v>
       </c>
     </row>
     <row r="53">
@@ -2276,28 +2276,28 @@
         <v>84</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8867761452031115</v>
+        <v>0.8841832324978393</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9221501390176089</v>
+        <v>0.9211502782931354</v>
       </c>
       <c r="F53" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9529750479846449</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9382366808109383</v>
+        <v>0.9367924528301886</v>
       </c>
       <c r="H53" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J53" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="54">
@@ -2311,28 +2311,28 @@
         <v>126</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8876404494382022</v>
+        <v>0.8772687986171133</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9230055658627088</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F54" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9500959692898272</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9386792452830188</v>
+        <v>0.9330819981149858</v>
       </c>
       <c r="H54" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I54" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J54" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K54" t="n">
-        <v>995</v>
+        <v>990</v>
       </c>
     </row>
     <row r="55">
@@ -2346,28 +2346,28 @@
         <v>168</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8841832324978393</v>
+        <v>0.8772687986171133</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9219330855018587</v>
+        <v>0.9189944134078212</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9520153550863724</v>
+        <v>0.9472168905950096</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9367327667610954</v>
+        <v>0.9328922495274102</v>
       </c>
       <c r="H55" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I55" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K55" t="n">
-        <v>992</v>
+        <v>987</v>
       </c>
     </row>
     <row r="56">
@@ -2381,28 +2381,28 @@
         <v>210</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8867761452031115</v>
+        <v>0.8789974070872947</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9205909510618652</v>
+        <v>0.9214953271028037</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9568138195777351</v>
+        <v>0.946257197696737</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9383529411764706</v>
+        <v>0.9337121212121212</v>
       </c>
       <c r="H56" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I56" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J56" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K56" t="n">
-        <v>997</v>
+        <v>986</v>
       </c>
     </row>
     <row r="57">
@@ -2416,28 +2416,28 @@
         <v>252</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8807260155574762</v>
+        <v>0.8772687986171133</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9200743494423792</v>
+        <v>0.9182156133828996</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9500959692898272</v>
+        <v>0.9481765834932822</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9348441926345609</v>
+        <v>0.9329556185080264</v>
       </c>
       <c r="H57" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I57" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J57" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K57" t="n">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="58">
@@ -2451,28 +2451,28 @@
         <v>294</v>
       </c>
       <c r="D58" t="n">
-        <v>0.88504753673293</v>
+        <v>0.8893690579083837</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9212233549582948</v>
+        <v>0.9247211895910781</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9539347408829175</v>
+        <v>0.95489443378119</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9372937293729373</v>
+        <v>0.939565627950897</v>
       </c>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I58" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J58" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K58" t="n">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="59">
@@ -2489,25 +2489,25 @@
         <v>0.8867761452031115</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9221501390176089</v>
+        <v>0.9213691026827012</v>
       </c>
       <c r="F59" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9558541266794626</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9382366808109383</v>
+        <v>0.9382948657560056</v>
       </c>
       <c r="H59" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I59" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J59" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K59" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="60">
@@ -2521,28 +2521,28 @@
         <v>378</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8841832324978393</v>
+        <v>0.8867761452031115</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9188191881918819</v>
+        <v>0.9221501390176089</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9558541266794626</v>
+        <v>0.95489443378119</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9369708372530574</v>
+        <v>0.9382366808109383</v>
       </c>
       <c r="H60" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I60" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J60" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K60" t="n">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61">
@@ -2556,16 +2556,16 @@
         <v>420</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8867761452031115</v>
+        <v>0.8833189282627485</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9213691026827012</v>
+        <v>0.9210770659238626</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9558541266794626</v>
+        <v>0.9520153550863724</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9382948657560056</v>
+        <v>0.9362907031618688</v>
       </c>
       <c r="H61" t="n">
         <v>30</v>
@@ -2574,10 +2574,10 @@
         <v>85</v>
       </c>
       <c r="J61" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="62">
@@ -2591,28 +2591,28 @@
         <v>42</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8980121002592912</v>
+        <v>0.891961970613656</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9293680297397769</v>
+        <v>0.9265116279069767</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9596928982725528</v>
+        <v>0.9558541266794626</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9442870632672332</v>
+        <v>0.9409541804440246</v>
       </c>
       <c r="H62" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I62" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J62" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K62" t="n">
-        <v>1000</v>
+        <v>996</v>
       </c>
     </row>
     <row r="63">
@@ -2626,28 +2626,28 @@
         <v>84</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8997407087294728</v>
+        <v>0.8936905790838375</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9294990723562152</v>
+        <v>0.9274418604651162</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9616122840690979</v>
+        <v>0.9568138195777351</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9452830188679245</v>
+        <v>0.9418989135569201</v>
       </c>
       <c r="H63" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I63" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J63" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K63" t="n">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="64">
@@ -2661,28 +2661,28 @@
         <v>126</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8980121002592912</v>
+        <v>0.8928262748487468</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9293680297397769</v>
+        <v>0.9281716417910447</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9596928982725528</v>
+        <v>0.95489443378119</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9442870632672332</v>
+        <v>0.9413434247871334</v>
       </c>
       <c r="H64" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I64" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J64" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="65">
@@ -2696,28 +2696,28 @@
         <v>168</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8971477960242005</v>
+        <v>0.8962834917891098</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9269195189639223</v>
+        <v>0.9284386617100372</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9616122840690979</v>
+        <v>0.9587332053742802</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9439472444653791</v>
+        <v>0.943342776203966</v>
       </c>
       <c r="H65" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I65" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J65" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K65" t="n">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="66">
@@ -2731,28 +2731,28 @@
         <v>210</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8971477960242005</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E66" t="n">
-        <v>0.927710843373494</v>
+        <v>0.9283720930232559</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9606525911708254</v>
+        <v>0.9577735124760077</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9438943894389439</v>
+        <v>0.9428436466698158</v>
       </c>
       <c r="H66" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I66" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J66" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K66" t="n">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="67">
@@ -2766,28 +2766,28 @@
         <v>252</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9014693171996543</v>
+        <v>0.8971477960242005</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9288354898336414</v>
+        <v>0.9293023255813954</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9644913627639156</v>
+        <v>0.9587332053742802</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9463276836158192</v>
+        <v>0.9437883797827114</v>
       </c>
       <c r="H67" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I67" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J67" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K67" t="n">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="68">
@@ -2801,22 +2801,22 @@
         <v>294</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9006050129645635</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9287696577243293</v>
+        <v>0.9296296296296296</v>
       </c>
       <c r="F68" t="n">
         <v>0.963531669865643</v>
       </c>
       <c r="G68" t="n">
-        <v>0.945831370701837</v>
+        <v>0.946277097078228</v>
       </c>
       <c r="H68" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I68" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J68" t="n">
         <v>38</v>
@@ -2839,25 +2839,25 @@
         <v>0.8945548833189283</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9275092936802974</v>
+        <v>0.9307116104868914</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9577735124760077</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9423984891406988</v>
+        <v>0.9421800947867298</v>
       </c>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I69" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J69" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K69" t="n">
-        <v>998</v>
+        <v>994</v>
       </c>
     </row>
     <row r="70">
@@ -2871,28 +2871,28 @@
         <v>378</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8962834917891098</v>
+        <v>0.891961970613656</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9276437847866419</v>
+        <v>0.9281045751633987</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9596928982725528</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9408424041646948</v>
       </c>
       <c r="H70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I70" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J70" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K70" t="n">
-        <v>1000</v>
+        <v>994</v>
       </c>
     </row>
     <row r="71">
@@ -2906,16 +2906,16 @@
         <v>420</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8980121002592912</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9293680297397769</v>
+        <v>0.9291705498602051</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9596928982725528</v>
+        <v>0.9568138195777351</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9442870632672332</v>
+        <v>0.9427895981087471</v>
       </c>
       <c r="H71" t="n">
         <v>39</v>
@@ -2924,10 +2924,10 @@
         <v>76</v>
       </c>
       <c r="J71" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K71" t="n">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="72">
@@ -2941,28 +2941,28 @@
         <v>42</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8997407087294728</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9263351749539595</v>
+        <v>0.9247015610651974</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9654510556621881</v>
+        <v>0.9664107485604606</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9454887218045113</v>
+        <v>0.9450961989676209</v>
       </c>
       <c r="H72" t="n">
+        <v>33</v>
+      </c>
+      <c r="I72" t="n">
+        <v>82</v>
+      </c>
+      <c r="J72" t="n">
         <v>35</v>
       </c>
-      <c r="I72" t="n">
-        <v>80</v>
-      </c>
-      <c r="J72" t="n">
-        <v>36</v>
-      </c>
       <c r="K72" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="73">
@@ -2976,22 +2976,22 @@
         <v>84</v>
       </c>
       <c r="D73" t="n">
-        <v>0.898876404494382</v>
+        <v>0.8954191875540191</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9254829806807727</v>
+        <v>0.922089825847846</v>
       </c>
       <c r="F73" t="n">
         <v>0.9654510556621881</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9450446218882105</v>
+        <v>0.943272386310361</v>
       </c>
       <c r="H73" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I73" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J73" t="n">
         <v>36</v>
@@ -3011,28 +3011,28 @@
         <v>126</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9014693171996543</v>
+        <v>0.902333621434745</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9233576642335767</v>
+        <v>0.9265381083562901</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9712092130518234</v>
+        <v>0.9683301343570058</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9466791393826005</v>
+        <v>0.9469732519943689</v>
       </c>
       <c r="H74" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I74" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J74" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K74" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="75">
@@ -3046,22 +3046,22 @@
         <v>168</v>
       </c>
       <c r="D75" t="n">
-        <v>0.898876404494382</v>
+        <v>0.8945548833189283</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9254829806807727</v>
+        <v>0.9212454212454212</v>
       </c>
       <c r="F75" t="n">
         <v>0.9654510556621881</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9450446218882105</v>
+        <v>0.9428303655107779</v>
       </c>
       <c r="H75" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I75" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J75" t="n">
         <v>36</v>
@@ -3081,28 +3081,28 @@
         <v>210</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8954191875540191</v>
+        <v>0.8962834917891098</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9244239631336405</v>
+        <v>0.9221611721611722</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9625719769673704</v>
+        <v>0.9664107485604606</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9431123648330982</v>
+        <v>0.943767572633552</v>
       </c>
       <c r="H76" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I76" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J76" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="77">
@@ -3116,28 +3116,28 @@
         <v>252</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8971477960242005</v>
+        <v>0.9014693171996543</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9245630174793008</v>
+        <v>0.9241316270566727</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9644913627639156</v>
+        <v>0.9702495201535508</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9441052137153593</v>
+        <v>0.9466292134831461</v>
       </c>
       <c r="H77" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I77" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J77" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K77" t="n">
-        <v>1005</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="78">
@@ -3154,25 +3154,25 @@
         <v>0.8936905790838375</v>
       </c>
       <c r="E78" t="n">
-        <v>0.922723091076357</v>
+        <v>0.9266480965645311</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9625719769673704</v>
+        <v>0.9577735124760077</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9422263973696571</v>
+        <v>0.9419537517697026</v>
       </c>
       <c r="H78" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I78" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J78" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K78" t="n">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="79">
@@ -3186,28 +3186,28 @@
         <v>336</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8954191875540191</v>
+        <v>0.8936905790838375</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9244239631336405</v>
+        <v>0.9250693802035153</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9625719769673704</v>
+        <v>0.9596928982725528</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9431123648330982</v>
+        <v>0.9420631182289213</v>
       </c>
       <c r="H79" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I79" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K79" t="n">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="80">
@@ -3221,28 +3221,28 @@
         <v>378</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8997407087294728</v>
+        <v>0.8936905790838375</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9263351749539595</v>
+        <v>0.922723091076357</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9654510556621881</v>
+        <v>0.9625719769673704</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9454887218045113</v>
+        <v>0.9422263973696571</v>
       </c>
       <c r="H80" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I80" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J80" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K80" t="n">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="81">
@@ -3256,28 +3256,28 @@
         <v>420</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8954191875540191</v>
+        <v>0.9006050129645635</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9236430542778289</v>
+        <v>0.9264029438822448</v>
       </c>
       <c r="F81" t="n">
-        <v>0.963531669865643</v>
+        <v>0.9664107485604606</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9431658055425082</v>
+        <v>0.9459840300610616</v>
       </c>
       <c r="H81" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I81" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J81" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K81" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="82">
@@ -3291,28 +3291,28 @@
         <v>42</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8927335640138409</v>
+        <v>0.8918685121107266</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9257884972170687</v>
+        <v>0.9289055191768008</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9577735124760077</v>
+        <v>0.9529750479846449</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9415094339622642</v>
+        <v>0.9407863571766935</v>
       </c>
       <c r="H82" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I82" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J82" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K82" t="n">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="83">
@@ -3326,16 +3326,16 @@
         <v>84</v>
       </c>
       <c r="D83" t="n">
-        <v>0.8927335640138409</v>
+        <v>0.8892733564013841</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9281716417910447</v>
+        <v>0.9279026217228464</v>
       </c>
       <c r="F83" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9510556621880998</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9413434247871334</v>
+        <v>0.9393364928909953</v>
       </c>
       <c r="H83" t="n">
         <v>37</v>
@@ -3344,10 +3344,10 @@
         <v>77</v>
       </c>
       <c r="J83" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K83" t="n">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="84">
@@ -3361,28 +3361,28 @@
         <v>126</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8944636678200693</v>
+        <v>0.8901384083044983</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9275092936802974</v>
+        <v>0.9255813953488372</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9577735124760077</v>
+        <v>0.95489443378119</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9423984891406988</v>
+        <v>0.940009447331129</v>
       </c>
       <c r="H84" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I84" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J84" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K84" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
     </row>
     <row r="85">
@@ -3396,28 +3396,28 @@
         <v>168</v>
       </c>
       <c r="D85" t="n">
-        <v>0.8918685121107266</v>
+        <v>0.8910034602076125</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9257195914577531</v>
+        <v>0.9272388059701493</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9568138195777351</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9410099103350638</v>
+        <v>0.9403973509933775</v>
       </c>
       <c r="H85" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I85" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J85" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K85" t="n">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="86">
@@ -3431,28 +3431,28 @@
         <v>210</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8901384083044983</v>
+        <v>0.8858131487889274</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9255813953488372</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="F86" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9481765834932822</v>
       </c>
       <c r="G86" t="n">
-        <v>0.940009447331129</v>
+        <v>0.9373814041745731</v>
       </c>
       <c r="H86" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I86" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J86" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K86" t="n">
-        <v>995</v>
+        <v>988</v>
       </c>
     </row>
     <row r="87">
@@ -3469,25 +3469,25 @@
         <v>0.8910034602076125</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9264432029795159</v>
+        <v>0.9272388059701493</v>
       </c>
       <c r="F87" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9404536862003781</v>
+        <v>0.9403973509933775</v>
       </c>
       <c r="H87" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I87" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J87" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K87" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="88">
@@ -3501,28 +3501,28 @@
         <v>294</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8892733564013841</v>
+        <v>0.8901384083044983</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9247211895910781</v>
+        <v>0.927170868347339</v>
       </c>
       <c r="F88" t="n">
-        <v>0.95489443378119</v>
+        <v>0.9529750479846449</v>
       </c>
       <c r="G88" t="n">
-        <v>0.939565627950897</v>
+        <v>0.9398958826313298</v>
       </c>
       <c r="H88" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I88" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J88" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K88" t="n">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="89">
@@ -3536,28 +3536,28 @@
         <v>336</v>
       </c>
       <c r="D89" t="n">
-        <v>0.8961937716262975</v>
+        <v>0.8910034602076125</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9268518518518518</v>
+        <v>0.9272388059701493</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9606525911708254</v>
+        <v>0.9539347408829175</v>
       </c>
       <c r="G89" t="n">
-        <v>0.943449575871819</v>
+        <v>0.9403973509933775</v>
       </c>
       <c r="H89" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I89" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J89" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K89" t="n">
-        <v>1001</v>
+        <v>994</v>
       </c>
     </row>
     <row r="90">
@@ -3571,28 +3571,28 @@
         <v>378</v>
       </c>
       <c r="D90" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.8953287197231834</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9293023255813954</v>
+        <v>0.9299719887955182</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9587332053742802</v>
+        <v>0.9558541266794626</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9437883797827114</v>
+        <v>0.9427354472314246</v>
       </c>
       <c r="H90" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I90" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J90" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K90" t="n">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="91">
@@ -3609,25 +3609,25 @@
         <v>0.8892733564013841</v>
       </c>
       <c r="E91" t="n">
-        <v>0.925512104283054</v>
+        <v>0.9271028037383178</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9539347408829175</v>
+        <v>0.9520153550863724</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9395085066162571</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="H91" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I91" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J91" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K91" t="n">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="92">
@@ -3641,28 +3641,28 @@
         <v>42</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9022491349480969</v>
+        <v>0.903114186851211</v>
       </c>
       <c r="E92" t="n">
-        <v>0.928110599078341</v>
+        <v>0.9313543599257885</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9664107485604606</v>
+        <v>0.963531669865643</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9468735307945463</v>
+        <v>0.9471698113207547</v>
       </c>
       <c r="H92" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I92" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J92" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K92" t="n">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="93">
@@ -3676,28 +3676,28 @@
         <v>84</v>
       </c>
       <c r="D93" t="n">
-        <v>0.903114186851211</v>
+        <v>0.9013840830449827</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9289667896678967</v>
+        <v>0.9296296296296296</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9664107485604606</v>
+        <v>0.963531669865643</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9473189087488241</v>
+        <v>0.946277097078228</v>
       </c>
       <c r="H93" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I93" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J93" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K93" t="n">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="94">
@@ -3711,28 +3711,28 @@
         <v>126</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9013840830449827</v>
+        <v>0.9048442906574394</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9304267161410018</v>
+        <v>0.9322820037105751</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9625719769673704</v>
+        <v>0.9644913627639156</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9462264150943396</v>
+        <v>0.9481132075471698</v>
       </c>
       <c r="H94" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I94" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J94" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K94" t="n">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="95">
@@ -3746,28 +3746,28 @@
         <v>168</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9005190311418685</v>
+        <v>0.9022491349480969</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9287696577243293</v>
+        <v>0.9312906220984215</v>
       </c>
       <c r="F95" t="n">
-        <v>0.963531669865643</v>
+        <v>0.9625719769673704</v>
       </c>
       <c r="G95" t="n">
-        <v>0.945831370701837</v>
+        <v>0.9466729589428976</v>
       </c>
       <c r="H95" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I95" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K95" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="96">
@@ -3781,28 +3781,28 @@
         <v>210</v>
       </c>
       <c r="D96" t="n">
-        <v>0.903114186851211</v>
+        <v>0.9013840830449827</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9281767955801105</v>
+        <v>0.9304267161410018</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9673704414587332</v>
+        <v>0.9625719769673704</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9462264150943396</v>
       </c>
       <c r="H96" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I96" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J96" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K96" t="n">
-        <v>1008</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="97">
@@ -3816,28 +3816,28 @@
         <v>252</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8987889273356401</v>
+        <v>0.9013840830449827</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9278445883441259</v>
+        <v>0.9312267657992565</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9625719769673704</v>
+        <v>0.9616122840690979</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9448893075836081</v>
+        <v>0.9461756373937678</v>
       </c>
       <c r="H97" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I97" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J97" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K97" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="98">
@@ -3851,22 +3851,22 @@
         <v>294</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9022491349480969</v>
+        <v>0.8996539792387543</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9304911955514366</v>
+        <v>0.9279112754158965</v>
       </c>
       <c r="F98" t="n">
         <v>0.963531669865643</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9467232437529467</v>
+        <v>0.9453860640301318</v>
       </c>
       <c r="H98" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I98" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J98" t="n">
         <v>38</v>
@@ -3886,28 +3886,28 @@
         <v>336</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9022491349480969</v>
+        <v>0.8979238754325259</v>
       </c>
       <c r="E99" t="n">
-        <v>0.928110599078341</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9664107485604606</v>
+        <v>0.9606525911708254</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9468735307945463</v>
+        <v>0.9443396226415094</v>
       </c>
       <c r="H99" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I99" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J99" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K99" t="n">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="100">
@@ -3921,28 +3921,28 @@
         <v>378</v>
       </c>
       <c r="D100" t="n">
-        <v>0.8996539792387543</v>
+        <v>0.9013840830449827</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9263351749539595</v>
+        <v>0.927255985267035</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9654510556621881</v>
+        <v>0.9664107485604606</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9454887218045113</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="H100" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I100" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J100" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K100" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="101">
@@ -3956,28 +3956,28 @@
         <v>420</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9100346020761245</v>
+        <v>0.8987889273356401</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9326568265682657</v>
+        <v>0.9270544783010157</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9702495201535508</v>
+        <v>0.963531669865643</v>
       </c>
       <c r="G101" t="n">
-        <v>0.9510818438381938</v>
+        <v>0.9449411764705883</v>
       </c>
       <c r="H101" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I101" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J101" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K101" t="n">
-        <v>1011</v>
+        <v>1004</v>
       </c>
     </row>
   </sheetData>
